--- a/diseases/d208/2010-2014.xlsx
+++ b/diseases/d208/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>23</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.4288364148492626</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>81</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>1.656725631099972</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>29</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.5407067839403746</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>38</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.7772293084172708</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>16</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.2983209842429653</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>79</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>1.6158188253938</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>15</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.27967592272778</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>57</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>1.165843962625906</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>28</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.5220617224251892</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>52</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>1.063576948360476</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>25</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.4661265378796332</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>71</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>1.452191602569111</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>13</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.2423857996974093</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>47</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.9613099340950453</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>23</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.4288364148492626</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>54</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>1.104483754066648</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>19</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.3542561687885213</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>71</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>1.452191602569111</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>27</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.5034166609100039</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>55</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>1.124937156919734</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>20</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.3729012303037066</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>59</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>1.206750768332078</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>13</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.2423857996974093</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>35</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.7158690998580125</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>28</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.5196501047373345</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>66</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>1.332534351120379</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>14</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.2598250523686673</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>51</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>1.029685634956656</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>21</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.3897375785530009</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>69</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>1.393104094353123</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>17</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.3155018493048102</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>49</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.9893058061348265</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>20</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.3711786462409532</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>54</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>1.090255378189401</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>16</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.2969429169927626</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>48</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.9691158917239119</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>24</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.4454143754891438</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>38</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.7672167476147636</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>19</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.3526197139289056</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>45</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.9085461484911672</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>24</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.4454143754891438</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>60</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>1.21139486465489</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>19</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.3526197139289056</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>76</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>1.534433495229527</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>12</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.2227071877445719</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>73</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>1.473863751996783</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>13</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.2412661200566196</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>42</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.8479764052584229</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>20</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.3694145785584575</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>56</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>1.115880726298868</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>13</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.2401194760629974</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>62</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>1.235439375545175</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>27</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.4987096810539177</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>53</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>1.056101401675714</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>23</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.4248267653422261</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>45</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.8966898693473045</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>15</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.2770609339188431</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>50</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.9963220770525606</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>22</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.4063560364143033</v>
       </c>
@@ -24129,9 +23952,6 @@
       <c r="O120" t="n">
         <v>55</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>1.095954284757817</v>
       </c>
@@ -24525,9 +24345,6 @@
       <c r="O122" t="n">
         <v>12</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.2216487471350745</v>
       </c>
@@ -24921,9 +24738,6 @@
       <c r="O124" t="n">
         <v>42</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.8369105447241508</v>
       </c>
@@ -25317,9 +25131,6 @@
       <c r="O126" t="n">
         <v>21</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.3878853074863803</v>
       </c>
@@ -25713,9 +25524,6 @@
       <c r="O128" t="n">
         <v>51</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>1.016248518593612</v>
       </c>
@@ -26109,9 +25917,6 @@
       <c r="O130" t="n">
         <v>28</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.5171804099818404</v>
       </c>
@@ -26505,9 +26310,6 @@
       <c r="O132" t="n">
         <v>50</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.9963220770525606</v>
       </c>
@@ -26901,9 +26703,6 @@
       <c r="O134" t="n">
         <v>20</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.3694145785584575</v>
       </c>
@@ -27297,9 +27096,6 @@
       <c r="O136" t="n">
         <v>67</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>1.335071583250431</v>
       </c>
@@ -27693,9 +27489,6 @@
       <c r="O138" t="n">
         <v>15</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.2770609339188431</v>
       </c>
@@ -28089,9 +27882,6 @@
       <c r="O140" t="n">
         <v>58</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>1.15573360938097</v>
       </c>
@@ -28485,9 +28275,6 @@
       <c r="O142" t="n">
         <v>12</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.2216487471350745</v>
       </c>
@@ -28881,9 +28668,6 @@
       <c r="O144" t="n">
         <v>43</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.8568369862652021</v>
       </c>
@@ -29277,9 +29061,6 @@
       <c r="O146" t="n">
         <v>18</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.330939963261987</v>
       </c>
@@ -29673,9 +29454,6 @@
       <c r="O148" t="n">
         <v>69</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>1.358234429097161</v>
       </c>
@@ -30069,9 +29847,6 @@
       <c r="O150" t="n">
         <v>23</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.4228677308347611</v>
       </c>
@@ -30465,9 +30240,6 @@
       <c r="O152" t="n">
         <v>61</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>1.200757973549664</v>
       </c>
@@ -30861,9 +30633,6 @@
       <c r="O154" t="n">
         <v>20</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.3677110702910966</v>
       </c>
@@ -31257,9 +31026,6 @@
       <c r="O156" t="n">
         <v>47</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.9251741763415444</v>
       </c>
@@ -31653,9 +31419,6 @@
       <c r="O158" t="n">
         <v>10</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.1838555351455483</v>
       </c>
@@ -32049,9 +31812,6 @@
       <c r="O160" t="n">
         <v>74</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>1.456657213814347</v>
       </c>
@@ -32445,9 +32205,6 @@
       <c r="O162" t="n">
         <v>24</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.441253284349316</v>
       </c>
@@ -32841,9 +32598,6 @@
       <c r="O164" t="n">
         <v>54</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>1.062966074945604</v>
       </c>
@@ -33237,9 +32991,6 @@
       <c r="O166" t="n">
         <v>18</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.330939963261987</v>
       </c>
@@ -33633,9 +33384,6 @@
       <c r="O168" t="n">
         <v>53</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>1.043281518002167</v>
       </c>
@@ -34029,9 +33777,6 @@
       <c r="O170" t="n">
         <v>13</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.2390121956892128</v>
       </c>
@@ -34425,9 +34170,6 @@
       <c r="O172" t="n">
         <v>41</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.8070668346809217</v>
       </c>
@@ -34821,9 +34563,6 @@
       <c r="O174" t="n">
         <v>22</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.4044821773202063</v>
       </c>
@@ -35217,9 +34956,6 @@
       <c r="O176" t="n">
         <v>51</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>1.003912404115293</v>
       </c>
@@ -35613,9 +35349,6 @@
       <c r="O178" t="n">
         <v>24</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.441253284349316</v>
       </c>
@@ -36009,9 +35742,6 @@
       <c r="O180" t="n">
         <v>68</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>1.338549872153724</v>
       </c>
@@ -36405,9 +36135,6 @@
       <c r="O182" t="n">
         <v>29</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.5331810519220901</v>
       </c>
@@ -36801,9 +36528,6 @@
       <c r="O184" t="n">
         <v>74</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>1.456657213814347</v>
       </c>
@@ -37197,9 +36921,6 @@
       <c r="O186" t="n">
         <v>23</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.4228677308347611</v>
       </c>
@@ -37593,9 +37314,6 @@
       <c r="O188" t="n">
         <v>60</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>1.181073416606227</v>
       </c>
@@ -37989,9 +37707,6 @@
       <c r="O190" t="n">
         <v>19</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.3493255167765418</v>
       </c>
@@ -38385,9 +38100,6 @@
       <c r="O192" t="n">
         <v>50</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.9842278471718557</v>
       </c>
@@ -38781,9 +38493,6 @@
       <c r="O194" t="n">
         <v>16</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.292949939981881</v>
       </c>
@@ -39177,9 +38886,6 @@
       <c r="O196" t="n">
         <v>51</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.9927210191157192</v>
       </c>
@@ -39573,9 +39279,6 @@
       <c r="O198" t="n">
         <v>16</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.292949939981881</v>
       </c>
@@ -39969,9 +39672,6 @@
       <c r="O200" t="n">
         <v>52</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>1.012186137137596</v>
       </c>
@@ -40365,9 +40065,6 @@
       <c r="O202" t="n">
         <v>18</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.3295686824796162</v>
       </c>
@@ -40761,9 +40458,6 @@
       <c r="O204" t="n">
         <v>66</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>1.284697789443872</v>
       </c>
@@ -41157,9 +40851,6 @@
       <c r="O206" t="n">
         <v>16</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.292949939981881</v>
       </c>
@@ -41553,9 +41244,6 @@
       <c r="O208" t="n">
         <v>43</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.8370000749407045</v>
       </c>
@@ -41949,9 +41637,6 @@
       <c r="O210" t="n">
         <v>11</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.2014030837375432</v>
       </c>
@@ -42345,9 +42030,6 @@
       <c r="O212" t="n">
         <v>48</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.9343256650500885</v>
       </c>
@@ -42741,9 +42423,6 @@
       <c r="O214" t="n">
         <v>25</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.4577342812216891</v>
       </c>
@@ -43137,9 +42816,6 @@
       <c r="O216" t="n">
         <v>59</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>1.148441963290734</v>
       </c>
@@ -43533,9 +43209,6 @@
       <c r="O218" t="n">
         <v>12</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.2197124549864108</v>
       </c>
@@ -43929,9 +43602,6 @@
       <c r="O220" t="n">
         <v>53</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>1.031651255159473</v>
       </c>
@@ -44325,9 +43995,6 @@
       <c r="O222" t="n">
         <v>24</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.4394249099728216</v>
       </c>
@@ -44721,9 +44388,6 @@
       <c r="O224" t="n">
         <v>50</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.9732559010938423</v>
       </c>
@@ -45117,9 +44781,6 @@
       <c r="O226" t="n">
         <v>37</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.6774467362080999</v>
       </c>
@@ -45513,9 +45174,6 @@
       <c r="O228" t="n">
         <v>60</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>1.167907081312611</v>
       </c>
@@ -45909,9 +45567,6 @@
       <c r="O230" t="n">
         <v>20</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.3661874249773513</v>
       </c>
@@ -46305,9 +45960,6 @@
       <c r="O232" t="n">
         <v>65</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>1.265232671421995</v>
       </c>
@@ -46701,9 +46353,6 @@
       <c r="O234" t="n">
         <v>25</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.4577342812216891</v>
       </c>
@@ -47097,9 +46746,6 @@
       <c r="O236" t="n">
         <v>67</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>1.304162907465749</v>
       </c>
@@ -47493,9 +47139,6 @@
       <c r="O238" t="n">
         <v>31</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.5675905087148946</v>
       </c>
@@ -47888,9 +47531,6 @@
       </c>
       <c r="O240" t="n">
         <v>57</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>1.10951172724698</v>
